--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>102.2374352358824</v>
+        <v>16.61358322583089</v>
       </c>
       <c r="D2" t="n">
-        <v>102.4219020896295</v>
+        <v>16.6435590895648</v>
       </c>
       <c r="E2" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F2" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.65493555185029</v>
+        <v>12.13142702717567</v>
       </c>
       <c r="D3" t="n">
-        <v>74.78065679805927</v>
+        <v>12.15185672968463</v>
       </c>
       <c r="E3" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F3" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.33357482639092</v>
+        <v>11.59170590928852</v>
       </c>
       <c r="D4" t="n">
-        <v>71.29121972603015</v>
+        <v>11.5848232054799</v>
       </c>
       <c r="E4" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F4" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.94945537714214</v>
+        <v>11.8542864987856</v>
       </c>
       <c r="D5" t="n">
-        <v>72.87269461163832</v>
+        <v>11.84181287439123</v>
       </c>
       <c r="E5" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F5" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>77.54445918015952</v>
+        <v>12.60097461677592</v>
       </c>
       <c r="D6" t="n">
-        <v>77.72037424079345</v>
+        <v>12.62956081412894</v>
       </c>
       <c r="E6" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F6" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>73.22456261254968</v>
+        <v>11.89899142453932</v>
       </c>
       <c r="D7" t="n">
-        <v>73.13478805667297</v>
+        <v>11.88440305920936</v>
       </c>
       <c r="E7" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F7" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>66.3987760030124</v>
+        <v>10.78980110048952</v>
       </c>
       <c r="D8" t="n">
-        <v>66.56097873950729</v>
+        <v>10.81615904516994</v>
       </c>
       <c r="E8" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F8" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>86.74233659252164</v>
+        <v>14.09562969628477</v>
       </c>
       <c r="D9" t="n">
-        <v>86.61768832774666</v>
+        <v>14.07537435325883</v>
       </c>
       <c r="E9" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F9" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>63.75363713063824</v>
+        <v>10.35996603372871</v>
       </c>
       <c r="D10" t="n">
-        <v>63.68664800205331</v>
+        <v>10.34908030033366</v>
       </c>
       <c r="E10" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F10" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>75.24309062727629</v>
+        <v>12.2270022269324</v>
       </c>
       <c r="D11" t="n">
-        <v>75.11953461609737</v>
+        <v>12.20692437511582</v>
       </c>
       <c r="E11" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F11" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>83.16179022216996</v>
+        <v>13.51379091110262</v>
       </c>
       <c r="D12" t="n">
-        <v>83.02564423204714</v>
+        <v>13.49166718770766</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F12" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.07130395068011</v>
+        <v>7.649086891985518</v>
       </c>
       <c r="D13" t="n">
-        <v>47.18676650799242</v>
+        <v>7.667849557548769</v>
       </c>
       <c r="E13" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F13" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>81.24950508056938</v>
+        <v>13.20304457559252</v>
       </c>
       <c r="D14" t="n">
-        <v>81.44844072866989</v>
+        <v>13.23537161840886</v>
       </c>
       <c r="E14" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F14" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>65.95043639153708</v>
+        <v>10.71694591362478</v>
       </c>
       <c r="D15" t="n">
-        <v>65.80307859120262</v>
+        <v>10.69300027107043</v>
       </c>
       <c r="E15" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F15" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.70315246514031</v>
+        <v>9.8642622755853</v>
       </c>
       <c r="D16" t="n">
-        <v>60.90501941954223</v>
+        <v>9.897065655675613</v>
       </c>
       <c r="E16" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F16" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>64.03975716178262</v>
+        <v>10.40646053878968</v>
       </c>
       <c r="D17" t="n">
-        <v>64.24518687857297</v>
+        <v>10.43984286776811</v>
       </c>
       <c r="E17" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F17" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.56896886953709</v>
+        <v>5.779957441299777</v>
       </c>
       <c r="D18" t="n">
-        <v>35.46362489138495</v>
+        <v>5.762839044850054</v>
       </c>
       <c r="E18" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F18" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>45.98338049534358</v>
+        <v>7.472299330493332</v>
       </c>
       <c r="D19" t="n">
-        <v>45.80982062581267</v>
+        <v>7.444095851694559</v>
       </c>
       <c r="E19" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F19" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>36.20190623619497</v>
+        <v>5.882809763381683</v>
       </c>
       <c r="D20" t="n">
-        <v>36.04123011346162</v>
+        <v>5.856699893437514</v>
       </c>
       <c r="E20" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F20" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>56.28569145041214</v>
+        <v>9.146424860691974</v>
       </c>
       <c r="D21" t="n">
-        <v>56.48986748650875</v>
+        <v>9.179603466557673</v>
       </c>
       <c r="E21" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F21" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>38.58894169638917</v>
+        <v>6.270703025663241</v>
       </c>
       <c r="D22" t="n">
-        <v>38.39456923710194</v>
+        <v>6.239117501029066</v>
       </c>
       <c r="E22" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F22" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>68.58555135302898</v>
+        <v>11.14515209486721</v>
       </c>
       <c r="D23" t="n">
-        <v>68.78734260355003</v>
+        <v>11.17794317307688</v>
       </c>
       <c r="E23" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F23" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>31.60521708356456</v>
+        <v>5.135847776079241</v>
       </c>
       <c r="D24" t="n">
-        <v>31.40663856125747</v>
+        <v>5.10357876620434</v>
       </c>
       <c r="E24" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F24" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>8.167437854316042</v>
+        <v>1.327208651326357</v>
       </c>
       <c r="D25" t="n">
-        <v>7.982228600376003</v>
+        <v>1.2971121475611</v>
       </c>
       <c r="E25" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F25" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>35.58818098770725</v>
+        <v>5.783079410502427</v>
       </c>
       <c r="D26" t="n">
-        <v>35.38138227717354</v>
+        <v>5.749474620040701</v>
       </c>
       <c r="E26" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F26" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72513213035479</v>
+        <v>2.392833971182653</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52909799929602</v>
+        <v>2.360978424885604</v>
       </c>
       <c r="E27" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F27" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>74.76358717127836</v>
+        <v>12.14908291533273</v>
       </c>
       <c r="D28" t="n">
-        <v>74.55588035187874</v>
+        <v>12.1153305571803</v>
       </c>
       <c r="E28" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F28" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>32.1400065114205</v>
+        <v>5.222751058105832</v>
       </c>
       <c r="D29" t="n">
-        <v>31.97293417099874</v>
+        <v>5.195601802787295</v>
       </c>
       <c r="E29" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F29" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>66.09655128250461</v>
+        <v>10.740689583407</v>
       </c>
       <c r="D30" t="n">
-        <v>50.39000391279073</v>
+        <v>8.188375635828494</v>
       </c>
       <c r="E30" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F30" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>71.63742418850434</v>
+        <v>11.64108143063196</v>
       </c>
       <c r="D31" t="n">
-        <v>46.47078056921379</v>
+        <v>7.551501842497242</v>
       </c>
       <c r="E31" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F31" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>48.26068071138688</v>
+        <v>7.842360615600369</v>
       </c>
       <c r="D32" t="n">
-        <v>48.31217353750564</v>
+        <v>7.850728199844666</v>
       </c>
       <c r="E32" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F32" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>63.26645905755452</v>
+        <v>10.28079959685261</v>
       </c>
       <c r="D33" t="n">
-        <v>39.24159138377374</v>
+        <v>6.376758599863233</v>
       </c>
       <c r="E33" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F33" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>72.08762226714602</v>
+        <v>11.71423861841123</v>
       </c>
       <c r="D34" t="n">
-        <v>29.9693910364053</v>
+        <v>4.870026043415861</v>
       </c>
       <c r="E34" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F34" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>70.43487778443431</v>
+        <v>11.44566763997057</v>
       </c>
       <c r="D35" t="n">
-        <v>45.56573084747351</v>
+        <v>7.404431262714446</v>
       </c>
       <c r="E35" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F35" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>81.24907788825075</v>
+        <v>13.20297515684075</v>
       </c>
       <c r="D36" t="n">
-        <v>23.19104946736567</v>
+        <v>3.768545538446922</v>
       </c>
       <c r="E36" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F36" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>94.13974537915772</v>
+        <v>15.29770862411313</v>
       </c>
       <c r="D37" t="n">
-        <v>9.551236357475092</v>
+        <v>1.552075908089703</v>
       </c>
       <c r="E37" t="n">
-        <v>21.1771563252166</v>
+        <v>3.441287902847697</v>
       </c>
       <c r="F37" t="n">
-        <v>22.72424010354468</v>
+        <v>3.69268901682601</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
